--- a/runs/rtdetr_v2_r18vd_from_scratch_26.05.2026/training_metrics.xlsx
+++ b/runs/rtdetr_v2_r18vd_from_scratch_26.05.2026/training_metrics.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1944,6 +1944,3345 @@
         <v>0.7905</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>6.0105</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>5.569161</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>6.040394</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.6398</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.7762</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>6.7618</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.000195</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>5.608413</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>6.174387</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.7308</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0.6405999999999999</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>7.5131</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0.000195</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>5.582248</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>5.94962</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0.7502</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>8.2645</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.000194</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>5.571993</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>6.159334</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.5506</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>9.0158</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0.000194</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>5.382148</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>5.869042</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.6519</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.7278</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.8095</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>9.767099999999999</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>5.538802</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5.982424</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0.6323</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>10.5184</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>5.408496</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>5.670232</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>11.2697</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0.000192</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>5.46048</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5.852146</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.7216</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0.7448</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>12.021</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0.000192</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>5.27793</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>5.778978</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0.4739</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0.6268</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.7358</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>12.7724</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>5.297621</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>6.025418</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.6374</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0.4756</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.7319</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>0.7619</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>13.5237</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>5.329433</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>5.543978</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.6459</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>14.275</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5.315955</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>5.877515</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.7171999999999999</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>0.7667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>15.0263</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5.193192</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5.962992</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.6277</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0.7714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>15.7776</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.000189</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5.281526</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5.664587</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.6168</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>0.6905</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>16.5289</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>44000</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0.000189</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>5.290203</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>5.951457</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.7423999999999999</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0.8238</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>17.2802</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0.000188</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>5.202617</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>5.718326</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.6616</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.6513</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.7288</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0.6346000000000001</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0.4957</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0.7469</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>18.0316</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0.000188</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5.220428</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>6.390295</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.6378</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0.5974</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0.7952</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>18.7829</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.000187</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>5.202321</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>5.853283</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.6593</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.4723</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>0.8095</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>19.5342</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0.000187</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5.191923</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>5.790182</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0.6893</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.7207</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0.6335</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0.7381</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>20.2855</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.000186</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5.28001</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>6.003086</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.7287</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.7183</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0.7337</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>21.0368</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>56000</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0.000186</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5.145162</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>6.110129</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>21.7881</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.000185</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5.261611</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>6.01959</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.6489</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.7374000000000001</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>0.7857</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>22.5394</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.000185</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5.305389</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>5.927824</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0.6581</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.7238</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>23.2908</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0.000184</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>5.100234</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>5.967138</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.6523</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.4817</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.6665</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0.6378</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>0.8429</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>24.0421</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>64000</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0.000184</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5.151143</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>5.70518</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.4829</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.6506</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0.7454</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0.8143</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>24.7934</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>66000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.000183</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>4.994365</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>5.717132</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.7216</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.7277</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0.4932</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>0.8143</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>25.5447</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>68000</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0.000183</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>5.069489</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>6.198564</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.7244</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>0.6371</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0.7456</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>26.296</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.000182</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5.061483</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5.941042</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.6945</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.6556</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.7282</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>0.8143</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>27.0473</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>72000</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0.000182</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>4.955929</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>6.030133</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0.7689</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.5864</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.6609</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0.7439</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0.6718</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0.8143</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>27.7986</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>74000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.000181</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5.01679</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5.992561</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>0.819</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>76000</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0.000181</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>4.994315</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>5.935496</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.5346</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.6486</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.7146</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0.7204</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0.8095</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>29.3013</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>78000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>5.119483</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>5.954908</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.7213000000000001</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0.6477000000000001</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>0.7306</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>0.7857</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>30.0526</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>4.958138</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>6.021899</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0.7513</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.6606</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0.6044</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>30.8039</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>82000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.000179</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>4.98554</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>5.968618</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0.7167</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.6747</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.7485000000000001</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>0.7428</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>0.8524</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>31.5552</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>84000</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.000179</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>5.065515</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>5.703823</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.7204</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>0.6373</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0.7286</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0.7952</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>32.3065</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>86000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.000178</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>4.926885</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>6.163192</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.7114</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0.6266</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>0.7667</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>33.0579</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>88000</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0.000178</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>5.051533</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>6.112235</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.6448</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>33.8092</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0.000177</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5.048257</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>6.135858</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.6138</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.7131</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>0.7714</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>34.5605</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>92000</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0.000177</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>4.966371</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>6.183337</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.7194</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>35.3118</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>94000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.000176</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4.758018</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>6.012227</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.6846</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.5174</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.7294</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>0.6506</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>0.7329</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>36.0631</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>96000</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0.000176</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>4.909525</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>5.801063</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.6472</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.7216</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>36.8144</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>4.844001</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>5.942547</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.5216</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.7272</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>0.6482</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>37.5657</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0.000199</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>4.978165</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>5.940456</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.6431</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0.7714</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>37.5657</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.000199</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>4.925512</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5.943861</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.6757</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>0.6496</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>0.7952</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>38.3171</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>102000</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0.000199</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>4.874422</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>6.087722</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0.7244</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0.7291</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>39.0684</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0.000198</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>4.881895</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>6.180308</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.6435999999999999</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.7134</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>39.8197</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>106000</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0.000198</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>5.051093</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>6.126947</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.6424</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>0.7323</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>40.571</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>108000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.000197</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4.86107</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>6.296438</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.7305</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>0.819</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>41.3223</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0.000197</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>4.899641</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>6.13481</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0.6421</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0.4852</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.7241</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0.8095</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>42.0736</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>112000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>4.859488</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>6.095186</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.6912</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>0.7316</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>42.8249</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>114000</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>4.955425</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>5.917893</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0.6894</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.6569</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>0.6224</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0.8238</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>43.5763</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>116000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0.000195</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>4.939596</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>5.843225</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.6887</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.6482</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.7163</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0.6218</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>0.819</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>44.3276</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>118000</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0.000195</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>4.973408</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>5.983027</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.6261</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>0.6088</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>0.7103</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>45.0789</v>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0.000194</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>4.929591</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>5.853645</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.6415</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>0.8048</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45.8302</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>122000</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0.000194</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>4.858897</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>5.817096</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0.7312</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0.5397</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.6425</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.7099</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>0.7223000000000001</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0.7667</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46.5815</v>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>124000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>4.83384</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>6.081921</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.4955</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>0.6489</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>0.7905</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>47.3328</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>126000</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4.825881</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>5.994069</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.4582</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0.6877</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.7305</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>0.7327</v>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0.8095</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>48.0841</v>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.000192</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>4.749806</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>6.024725</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.6561</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0.7252999999999999</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>0.7271</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>0.7952</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>48.8355</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>130000</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>0.000192</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>4.834059</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>6.019823</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>49.5868</v>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>132000</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>4.839629</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>5.990249</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.7028</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>0.6477000000000001</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>0.7286</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>50.3381</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>134000</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>4.861975</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>5.869773</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0.6773</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>0.7192</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0.7952</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>51.0894</v>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>136000</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>4.783169</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>6.055695</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.6409</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>0.7062</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>51.8407</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>138000</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>4.809332</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>6.118311</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.6456</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.7181999999999999</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>0.7274</v>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
